--- a/reports/تكلفة_حرق_قطاف.xlsx
+++ b/reports/تكلفة_حرق_قطاف.xlsx
@@ -632,11 +632,11 @@
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>نسبة خصم قطاف (2% العنوان / 5% المثال)</t>
+          <t>نسبة خصم قطاف (مؤكّدة 2%)</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
